--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\OneDrive\Documents\Internship\Business-Listing\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -111,10 +111,16 @@
     <t xml:space="preserve">Backend Developer — Business Listing </t>
   </si>
   <si>
+    <t>1.  feat: draft Business, Review, Booking models with relations (pending supervisor approval)          2. docs: add ERD for Business, Review, Booking schema (pending approval)                            3. docs: mention docs/ folder in root README     4. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
     <t>1. chore: add starter project structure (auth module implemented; listings, reviews, bookings scaffolded)
-2. chore: F11restructure repo into backend/ and frontend/ monorepo H7layout
+2. chore: F11restructure repo into backend/ and frontend/ monorepo layout
 3. chore: approve install scripts, add lockfile and initial User migration
 4. chore: switch backend port to 3001 to avoid clash with frontend default             5. Removed guideline document                          6. Deleted Backend-Dev5-Guideline.docx                 7. docs: add daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Drafted Business/Review/Booking schema with relations, created ERD, sent for approval                     Discussions on the project with the CEO and frontend developer to better understand the requirements      Updated Trello according to the status of the tasks</t>
   </si>
 </sst>
 </file>
@@ -207,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -226,6 +232,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -575,28 +584,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
     </row>
     <row r="4" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -644,24 +653,32 @@
         <v>26</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="159" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="5">
+        <v>46260</v>
+      </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -121,6 +121,15 @@
   </si>
   <si>
     <t>Drafted Business/Review/Booking schema with relations, created ERD, sent for approval                     Discussions on the project with the CEO and frontend developer to better understand the requirements      Updated Trello according to the status of the tasks</t>
+  </si>
+  <si>
+    <t>Ran the Prisma migration for the new models, Verified the migration in Prisma Studio, Resolved a Git sync conflict, Had a meeting with the frontend developer where we discussed ideas and checking the website design, Researched and planned the process of turning listings.service.ts from a stub to an actual working CRUD logic</t>
+  </si>
+  <si>
+    <t>Brief Git sync conflict with teammate's push, resolved cleanly</t>
+  </si>
+  <si>
+    <t>1. feat: migrate Business, Review, Booking tables        2. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
@@ -681,19 +690,29 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="5">
+        <v>46261</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
+      <c r="D7" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="34">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -57,46 +57,22 @@
     <t>Week 2</t>
   </si>
   <si>
-    <t>Homepage — build every section</t>
-  </si>
-  <si>
     <t>Week 3</t>
   </si>
   <si>
-    <t>Inner pages (first batch)</t>
-  </si>
-  <si>
     <t>Week 4</t>
   </si>
   <si>
-    <t>Remaining inner pages + finish the 3 required components</t>
-  </si>
-  <si>
     <t>Week 5</t>
   </si>
   <si>
-    <t>Dashboard / modules (if applicable to this project)</t>
-  </si>
-  <si>
     <t>Week 6</t>
   </si>
   <si>
-    <t>Interactivity, form validation, state management</t>
-  </si>
-  <si>
     <t>Week 7</t>
   </si>
   <si>
-    <t>Wire up config for dynamic content + responsive QA</t>
-  </si>
-  <si>
     <t>Week 8</t>
-  </si>
-  <si>
-    <t>Bug fixing, content polish, deployment, final presentation</t>
-  </si>
-  <si>
-    <t>Set node/npm/nest cSet up Node, npm, and Nest CLI. Set up proper git branches, pushed the starter files. Got PostgreSQL running in Docker and connected it to Prisma. Ran the migration and got the User table created. Tested the full auth flow with curl i.e. register, login, and the protected /me route all working with JWT. Also restructured the repo into backend/ and frontend/ folders, and set up a Trello board for tracking tasks going forward.li</t>
   </si>
   <si>
     <t>8 hours</t>
@@ -130,6 +106,24 @@
   </si>
   <si>
     <t>1. feat: migrate Business, Review, Booking tables        2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Set node/npm/nest cli Set up Node, npm, and Nest CLI. Set up proper git branches, pushed the starter files. Got PostgreSQL running in Docker and connected it to Prisma. Ran the migration and got the User table created. Tested the full auth flow with curl i.e. register, login, and the protected /me route all working with JWT. Also restructured the repo into backend/ and frontend/ folders, and set up a Trello board for tracking tasks going forward.</t>
+  </si>
+  <si>
+    <t>Kickoff meeting, assigned the Universal Business Listing Theme API project (NestJS + Prisma + PostgreSQL). Reviewed the project guideline and starter files to understand scope before starting setup. Learned basics of NestJS, Prisma and PostgreSQL</t>
+  </si>
+  <si>
+    <t>5 hours</t>
+  </si>
+  <si>
+    <t>9 hours</t>
+  </si>
+  <si>
+    <t>Implemented Listings module CRUD logic; discovered listings need admin approval, added status field and approval workflow, tested end-to-end</t>
+  </si>
+  <si>
+    <t>1. feat: implement Listings module with admin approval workflow               2. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
@@ -594,7 +588,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -642,104 +636,118 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="290.39999999999998" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="66" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="159" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" ht="291" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="92.4" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="5">
+        <v>46261</v>
+      </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="66" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="5">
+        <v>46262</v>
+      </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
+      <c r="D9" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="E9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -750,9 +758,7 @@
       <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
@@ -822,11 +828,9 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
@@ -890,17 +894,15 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>16</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D20" s="3"/>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
@@ -970,11 +972,9 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D25" s="3"/>
       <c r="E25" s="2" t="s">
         <v>10</v>
       </c>
@@ -1044,11 +1044,9 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D30" s="3"/>
       <c r="E30" s="2" t="s">
         <v>10</v>
       </c>
@@ -1118,11 +1116,9 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D35" s="3"/>
       <c r="E35" s="2" t="s">
         <v>10</v>
       </c>
@@ -1186,17 +1182,15 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>36</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>24</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D40" s="3"/>
       <c r="E40" s="2" t="s">
         <v>10</v>
       </c>

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -124,6 +124,16 @@
   </si>
   <si>
     <t>1. feat: implement Listings module with admin approval workflow               2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>8/31/20226</t>
+  </si>
+  <si>
+    <t>Extracted admin role check into RolesGuard/@Roles decorator, fixed a file-path mixup, tested full approval workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. refactor: extract admin role check into RolesGuard and @Roles decorator                          2. docs: added daily tracker spreadsheet
+</t>
   </si>
 </sst>
 </file>
@@ -750,20 +760,28 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>6</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="E10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -132,7 +132,7 @@
     <t>Extracted admin role check into RolesGuard/@Roles decorator, fixed a file-path mixup, tested full approval workflow</t>
   </si>
   <si>
-    <t xml:space="preserve">1. refactor: extract admin role check into RolesGuard and @Roles decorator                          2. docs: added daily tracker spreadsheet
+    <t xml:space="preserve">1. refactor: extract admin role check into RolesGuard and @Roles decorator                          2. docs: added daily tracker spreadsheet 
 </t>
   </si>
 </sst>

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="40">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -134,6 +134,16 @@
   <si>
     <t xml:space="preserve">1. refactor: extract admin role check into RolesGuard and @Roles decorator                          2. docs: added daily tracker spreadsheet 
 </t>
+  </si>
+  <si>
+    <t>Verified full forgot/reset-password flow; added contact fields + coordinates to Business schema; built and debugged distance-based nearby search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. feat: add contact fields and coordinates to Business; support distance-based nearby search                               2. docs: added daily tracker spreadsheet 
+</t>
+  </si>
+  <si>
+    <t>Second schema addendum needed — added contact/coordinate fields after the original approval, same as the status field earlier</t>
   </si>
 </sst>
 </file>
@@ -784,19 +794,29 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="5">
+        <v>46266</v>
+      </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="E11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>Second schema addendum needed — added contact/coordinate fields after the original approval, same as the status field earlier</t>
+  </si>
+  <si>
+    <t>Implemented real email sending for forgot-password using Nodemailer + Ethereal, replacing the TODO placeholder; tested full flow end-to-end</t>
+  </si>
+  <si>
+    <t>1. feat: implement real email sending for forgot-password using Nodemailer                        2. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
@@ -818,18 +824,26 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="5">
+        <v>46267</v>
+      </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="E12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>1. feat: implement real email sending for forgot-password using Nodemailer                        2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Added isPartner field and computed review count to Business; designed and migrated a new Product model based on frontend/supervisor's SaaS integration plans</t>
+  </si>
+  <si>
+    <t>1. feat: add isPartner field, review count, and Product model to schema               2. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
@@ -846,18 +852,26 @@
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="66" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="5">
+        <v>46268</v>
+      </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="E13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -156,6 +156,12 @@
   </si>
   <si>
     <t>1. feat: add isPartner field, review count, and Product model to schema               2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Built Product module DTOs and partial service which included the create and findAll</t>
+  </si>
+  <si>
+    <t>1. feat: add Product DTOs and partial service (create, findAll) - controller and remaining CRUD pending                            2. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
@@ -874,18 +880,26 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>10</v>
       </c>
-      <c r="B14" s="3"/>
+      <c r="B14" s="5">
+        <v>46269</v>
+      </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
+      <c r="D14" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="E14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="48">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -162,13 +162,19 @@
   </si>
   <si>
     <t>1. feat: add Product DTOs and partial service (create, findAll) - controller and remaining CRUD pending                            2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Completed the Product module — finished remaining CRUD methods, added controller and module wiring, tested full flow end-to-end including ownership enforcement</t>
+  </si>
+  <si>
+    <t>1. feat: complete Product module - controller, module wiring, full CRUD with ownership checks        2. docs: added daily tracker spreadsheet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +210,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -254,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -280,6 +292,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,20 +917,28 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>11</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="5">
+        <v>46272</v>
+      </c>
       <c r="C15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="E15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -168,6 +168,15 @@
   </si>
   <si>
     <t>1. feat: complete Product module - controller, module wiring, full CRUD with ownership checks        2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Paused NestJS Business Listing API work per supervisor's request. Set up local WordPress + WooCommerce environment (Local by WP Engine) for Namaste Dining restaurant menu digitization. Extracted full menu (151 items) from photos into structured spreadsheet, set up 28 product categories, and began entering products (60+ published so far — simple and variable products with EN/JP bilingual naming)</t>
+  </si>
+  <si>
+    <t>1. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -266,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -289,12 +298,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,28 +652,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
     </row>
     <row r="4" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -927,7 +939,7 @@
       <c r="C15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -941,18 +953,26 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>12</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="9">
+        <v>46273</v>
+      </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="3"/>
+      <c r="D16" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="E16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="51">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -176,7 +176,7 @@
     <t>1. docs: added daily tracker spreadsheet</t>
   </si>
   <si>
-    <t>In Progress</t>
+    <t>Completed WooCommerce product entry for Namaste Dining menu — all 151 menu items now published (126 simple products, 14 variable products with size/flavor/tier variations, e.g. Chicken Tikka 2P/4P, Foreign Beer flavor choice, A Set/B Set curry-only vs full-set tiers). Resolved 4 previously-flagged price/data conflicts per supervisor's guidance (Malai Tikka, Garlic Nan, Spinach Nan, Biryani #03)</t>
   </si>
 </sst>
 </file>
@@ -965,7 +965,7 @@
         <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>18</v>
@@ -975,18 +975,26 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>13</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="5">
+        <v>46274</v>
+      </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="3"/>
+      <c r="D17" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="E17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="52">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -170,13 +170,16 @@
     <t>1. feat: complete Product module - controller, module wiring, full CRUD with ownership checks        2. docs: added daily tracker spreadsheet</t>
   </si>
   <si>
-    <t>Paused NestJS Business Listing API work per supervisor's request. Set up local WordPress + WooCommerce environment (Local by WP Engine) for Namaste Dining restaurant menu digitization. Extracted full menu (151 items) from photos into structured spreadsheet, set up 28 product categories, and began entering products (60+ published so far — simple and variable products with EN/JP bilingual naming)</t>
-  </si>
-  <si>
     <t>1. docs: added daily tracker spreadsheet</t>
   </si>
   <si>
-    <t>Completed WooCommerce product entry for Namaste Dining menu — all 151 menu items now published (126 simple products, 14 variable products with size/flavor/tier variations, e.g. Chicken Tikka 2P/4P, Foreign Beer flavor choice, A Set/B Set curry-only vs full-set tiers). Resolved 4 previously-flagged price/data conflicts per supervisor's guidance (Malai Tikka, Garlic Nan, Spinach Nan, Biryani #03)</t>
+    <t>Paused NestJS Business Listing API work per supervisor's request. Installed and configured local WordPress + WooCommerce environment (Local by WP Engine) for Namaste Dining restaurant menu digitization — fixed currency to Japanese Yen, set up 28 product categories (including parent/child structure for Drinks and Takeout sub-categories). Extracted full menu (151 items) from 30 menu photos into a structured reference spreadsheet (English/Japanese names, prices, categories, descriptions). Began WooCommerce product entry using this sheet — published first ~60 products (simple products with bilingual EN/JP naming, tax-included pricing, category tagging, and cropped item photos).</t>
+  </si>
+  <si>
+    <t>Continued and completed WooCommerce product entry for the remaining ~90 menu items, bringing the full Namaste Dining menu to all 151 items published. Set up 14 variable products for items with size/flavor/tier options (e.g. Chicken Tikka 2P/4P, Foreign Beer flavor choice, A Set/B Set curry-only vs. full-set pricing tiers) using WooCommerce attributes and variations. Identified and corrected a data-entry issue where A Set and B Set had been entered as separate simple products instead of one variable product per set. Flagged 4 items with conflicting prices across source menu photos (Malai Tikka, Garlic Nan, Spinach Nan, Biryani #03) to supervisor and resolved all 4 once he confirmed the approach to use.</t>
+  </si>
+  <si>
+    <t>Ran a full data QA pass on the published WooCommerce catalog (via product export CSV) against the source spreadsheet — checked for missing prices, missing categories, missing products, and missing images across all 151 items. Found and fixed 2 accidentally-skipped products (Rum Khukri Rock, Rum Cola) and an incomplete variable product (Sour was missing 4 of its 6 flavor variations). Sourced and uploaded product images for the remaining items, including cropping individual dish photos out of shared menu-page images (Chowmien, lassi flavors) and sourcing free-license generic bottle photos (Unsplash) for branded alcohol items where using the real product photo would raise trademark/copyright concerns. Menu digitization task is now effectively complete pending final image cleanup (4 images remaining) and a wrap-up check-in with supervisor.</t>
   </si>
 </sst>
 </file>
@@ -953,7 +956,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -962,7 +965,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>20</v>
@@ -971,11 +974,11 @@
         <v>18</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" ht="105.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="184.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -993,22 +996,30 @@
         <v>18</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="224.4" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>14</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="5">
+        <v>46275</v>
+      </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="3"/>
+      <c r="D18" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="E18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">

--- a/backend/Backend-Dev3-Daily-Tracker.xlsx
+++ b/backend/Backend-Dev3-Daily-Tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="55">
   <si>
     <t>40 Working Days · 8 Hours/Day · Fill in Date, Status, Hours, and Notes every day.</t>
   </si>
@@ -180,6 +180,15 @@
   </si>
   <si>
     <t>Ran a full data QA pass on the published WooCommerce catalog (via product export CSV) against the source spreadsheet — checked for missing prices, missing categories, missing products, and missing images across all 151 items. Found and fixed 2 accidentally-skipped products (Rum Khukri Rock, Rum Cola) and an incomplete variable product (Sour was missing 4 of its 6 flavor variations). Sourced and uploaded product images for the remaining items, including cropping individual dish photos out of shared menu-page images (Chowmien, lassi flavors) and sourcing free-license generic bottle photos (Unsplash) for branded alcohol items where using the real product photo would raise trademark/copyright concerns. Menu digitization task is now effectively complete pending final image cleanup (4 images remaining) and a wrap-up check-in with supervisor.</t>
+  </si>
+  <si>
+    <t>Started Reviews module — confirmed schema relations already existed, built CreateReviewDto/ReviewFilterDto, implemented paginated+sortable findByBusiness(), wired the nested GET route, tested clean boot + Postman</t>
+  </si>
+  <si>
+    <t>1. feat: add review DTOs and GET reviews endpoint                                     2. docs: added daily tracker spreadsheet</t>
+  </si>
+  <si>
+    <t>Flagged that POST/DELETE + rating recalculation are planned for tomorrow</t>
   </si>
 </sst>
 </file>
@@ -1022,19 +1031,29 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="66" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>15</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="5">
+        <v>46276</v>
+      </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="3"/>
+      <c r="D19" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="E19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
